--- a/Listing/FES03N.xlsx
+++ b/Listing/FES03N.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{E6BDD824-8285-D34A-AE81-4405D0222D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="294">
   <si>
     <t/>
   </si>
@@ -850,38 +867,62 @@
     <t>104</t>
   </si>
   <si>
+    <t>20140455</t>
+  </si>
+  <si>
+    <t>IDM STICK CKLT 18S</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>20140456</t>
+  </si>
+  <si>
+    <t>WONG COCO PEDAS 220G</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN PCS</t>
+  </si>
+  <si>
+    <t>FES04N</t>
+  </si>
+  <si>
+    <t>PT,(E-2H)</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN 250</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20140455</t>
-  </si>
-  <si>
-    <t>IDM STICK CKLT 18S</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
-  </si>
-  <si>
-    <t>106</t>
+    <t>KRM TUNISIA HIJRA500</t>
+  </si>
+  <si>
+    <t>KURMA TUNIS BRARI500</t>
+  </si>
+  <si>
+    <t>KURMA MEDJOOL  PCK</t>
+  </si>
+  <si>
+    <t>KURMA SAYER BRARI250</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -902,16 +943,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1260,19 +1301,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F93"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F100"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="1" max="1" width="9.953125" customWidth="1"/>
+    <col min="2" max="2" width="22.05859375" customWidth="1"/>
+    <col min="3" max="3" width="7.93359375" customWidth="1"/>
+    <col min="4" max="4" width="2.95703125" customWidth="1"/>
+    <col min="5" max="5" width="4.9765625" customWidth="1"/>
+    <col min="6" max="6" width="13.046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1312,7 +1353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1332,7 +1373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1352,7 +1393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1372,7 +1413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1392,7 +1433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1412,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1432,7 +1473,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,7 +1493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1472,7 +1513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -1492,7 +1533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1512,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1532,7 +1573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -1552,7 +1593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -1572,7 +1613,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -1592,7 +1633,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -1612,7 +1653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>53</v>
       </c>
@@ -1632,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1652,7 +1693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
@@ -1672,7 +1713,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
@@ -1692,7 +1733,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -1712,7 +1753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>69</v>
       </c>
@@ -1732,7 +1773,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>72</v>
       </c>
@@ -1752,7 +1793,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>76</v>
       </c>
@@ -1772,7 +1813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>79</v>
       </c>
@@ -1792,7 +1833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -1812,7 +1853,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
@@ -1832,7 +1873,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>88</v>
       </c>
@@ -1852,7 +1893,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -1872,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
@@ -1892,7 +1933,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
@@ -1912,7 +1953,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>100</v>
       </c>
@@ -1932,7 +1973,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>104</v>
       </c>
@@ -1952,7 +1993,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>107</v>
       </c>
@@ -1972,7 +2013,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
@@ -1992,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>113</v>
       </c>
@@ -2012,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>116</v>
       </c>
@@ -2032,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>119</v>
       </c>
@@ -2052,7 +2093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>122</v>
       </c>
@@ -2072,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>125</v>
       </c>
@@ -2092,7 +2133,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>129</v>
       </c>
@@ -2112,7 +2153,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>132</v>
       </c>
@@ -2132,7 +2173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>135</v>
       </c>
@@ -2152,7 +2193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
@@ -2172,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>141</v>
       </c>
@@ -2192,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>144</v>
       </c>
@@ -2212,7 +2253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>147</v>
       </c>
@@ -2232,7 +2273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -2252,7 +2293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>153</v>
       </c>
@@ -2272,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>156</v>
       </c>
@@ -2292,7 +2333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>159</v>
       </c>
@@ -2312,7 +2353,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>162</v>
       </c>
@@ -2332,7 +2373,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>165</v>
       </c>
@@ -2352,7 +2393,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>168</v>
       </c>
@@ -2372,7 +2413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>171</v>
       </c>
@@ -2392,7 +2433,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>174</v>
       </c>
@@ -2412,7 +2453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>177</v>
       </c>
@@ -2432,7 +2473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>180</v>
       </c>
@@ -2452,7 +2493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>183</v>
       </c>
@@ -2472,7 +2513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>186</v>
       </c>
@@ -2492,7 +2533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>189</v>
       </c>
@@ -2512,7 +2553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>192</v>
       </c>
@@ -2532,7 +2573,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>195</v>
       </c>
@@ -2552,7 +2593,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>198</v>
       </c>
@@ -2572,7 +2613,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>201</v>
       </c>
@@ -2592,7 +2633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>204</v>
       </c>
@@ -2612,7 +2653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>207</v>
       </c>
@@ -2632,7 +2673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>210</v>
       </c>
@@ -2652,7 +2693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>213</v>
       </c>
@@ -2672,7 +2713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>216</v>
       </c>
@@ -2692,7 +2733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>219</v>
       </c>
@@ -2712,7 +2753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>222</v>
       </c>
@@ -2732,7 +2773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>225</v>
       </c>
@@ -2752,7 +2793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>228</v>
       </c>
@@ -2772,7 +2813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>231</v>
       </c>
@@ -2792,7 +2833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>234</v>
       </c>
@@ -2812,7 +2853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>237</v>
       </c>
@@ -2832,7 +2873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>240</v>
       </c>
@@ -2852,7 +2893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>243</v>
       </c>
@@ -2872,7 +2913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>246</v>
       </c>
@@ -2892,7 +2933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>249</v>
       </c>
@@ -2912,7 +2953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>252</v>
       </c>
@@ -2932,7 +2973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>255</v>
       </c>
@@ -2952,7 +2993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>258</v>
       </c>
@@ -2972,7 +3013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>261</v>
       </c>
@@ -2992,7 +3033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>264</v>
       </c>
@@ -3012,7 +3053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>267</v>
       </c>
@@ -3032,7 +3073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>270</v>
       </c>
@@ -3052,7 +3093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>273</v>
       </c>
@@ -3072,7 +3113,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>276</v>
       </c>
@@ -3089,51 +3130,171 @@
         <v>278</v>
       </c>
       <c r="F91" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="F92" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>20070380</v>
+      </c>
+      <c r="B95" t="s">
+        <v>285</v>
+      </c>
+      <c r="C95" t="s">
+        <v>286</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>20046368</v>
+      </c>
+      <c r="B96" t="s">
+        <v>288</v>
+      </c>
+      <c r="C96" t="s">
+        <v>286</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>20016388</v>
+      </c>
+      <c r="B97" t="s">
+        <v>290</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>20140218</v>
+      </c>
+      <c r="B98" t="s">
+        <v>291</v>
+      </c>
+      <c r="C98" t="s">
+        <v>286</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>20113971</v>
+      </c>
+      <c r="B99" t="s">
+        <v>292</v>
+      </c>
+      <c r="C99" t="s">
+        <v>286</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>20140192</v>
+      </c>
+      <c r="B100" t="s">
+        <v>293</v>
+      </c>
+      <c r="C100" t="s">
+        <v>286</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>6</v>
+      </c>
+      <c r="F100" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>